--- a/tools/_out/orfs_gen_20261020/out/DesignTable_FS6505_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/DesignTable_FS6505_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,155 +524,150 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>FSWB_CSANG@DRIVE</t>
+          <t>FSWB_MINR@DRIVE</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>FSWB_MINR@DRIVE</t>
+          <t>FSWB_THDL@DRIVE</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>FSWB_THDL@DRIVE</t>
+          <t>FSWB_RELANG@DRIVE</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>FSWB_RELANG@DRIVE</t>
+          <t>FSWB_RELR@DRIVE</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>FSWB_RELR@DRIVE</t>
+          <t>FSWB_STEMR@DRIVE</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>FSWB_STEMR@DRIVE</t>
+          <t>FSWB_HEADL@DRIVE</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>FSWB_HEADL@DRIVE</t>
+          <t>HELIXDIA@HELIXSK_B</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>HELIXDIA@HELIXSK_B</t>
+          <t>HEIGHT@HELIX_B</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>HEIGHT@HELIX_B</t>
+          <t>PITCH@HELIX_B</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>PITCH@HELIX_B</t>
+          <t>PROF_R@THDPROF_B</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>PROF_R@THDPROF_B</t>
+          <t>APEXR@THDPROF_B</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>APEXR@THDPROF_B</t>
+          <t>FSWB_CSR@DRIVE</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>FSWB_CSR@DRIVE</t>
+          <t>PROF_AX@THDPROF_B</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>PROF_AX@THDPROF_B</t>
+          <t>DA@BORE_A</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>DA@BORE_A</t>
+          <t>DEPTH@BORECUT_A</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT_A</t>
+          <t>DB@BORE_B</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>DB@BORE_B</t>
+          <t>DEPTH@BORECUT_B</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT_B</t>
+          <t>START@BORECUT_B</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>START@BORECUT_B</t>
+          <t>DEPTH@HEXCUT</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>DEPTH@HEXCUT</t>
+          <t>NUTHEX@NUTHEX</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>NUTHEX@NUTHEX</t>
+          <t>DEPTH@NUTCUT</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>DEPTH@NUTCUT</t>
+          <t>$PRP@PartNo</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>$PRP@PartNo</t>
+          <t>$PRP@Description</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>$PRP@Description</t>
+          <t>$PRP@GeometryRoot</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>$PRP@GeometryRoot</t>
+          <t>$PRP@EndA_Thread</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>$PRP@EndA_Thread</t>
+          <t>$PRP@EndB_Thread</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>$PRP@EndB_Thread</t>
+          <t>$PRP@DataStatus</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>$PRP@DataStatus</t>
+          <t>$PRP@AxialSource</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>$PRP@AxialSource</t>
+          <t>$COMMENT</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
-        <is>
-          <t>$COMMENT</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
         </is>
@@ -748,112 +743,109 @@
         <v>0.433</v>
       </c>
       <c r="W2" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="Y2" t="n">
         <v>45</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.7448399999999999</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0.37242</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0.36882</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.4165</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.3725</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.7448399999999999</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.4059</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.0625</v>
-      </c>
       <c r="AG2" t="n">
-        <v>0.37242</v>
+        <v>0.40625</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.40625</v>
+        <v>0.4095</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.4095</v>
+        <v>2.423</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.423</v>
+        <v>0.53</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.53</v>
+        <v>0.9425</v>
       </c>
       <c r="AL2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.0675</v>
+      </c>
+      <c r="AN2" t="n">
         <v>0.9425</v>
       </c>
-      <c r="AM2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.0675</v>
-      </c>
       <c r="AO2" t="n">
-        <v>0.9425</v>
+        <v>1.135</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.135</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AR2" t="n">
         <v>0.482</v>
       </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>FS6505-08-08</t>
+        </is>
+      </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>FS6505-08-08</t>
+          <t>ORFS Swivel Connector (female face-seal swivel x male pipe), 1/2-14 NPTF x 13/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>ORFS Swivel Connector (female face-seal swivel x male pipe), 1/2-14 NPTF x 13/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>FS6505</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>FS6505</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>13/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>13/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>Air-Way FF6505 (s485, double-pass 2026-10-15, parts.air-way.com/api/series/485, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6505-08-08 (ORFS-p006-t04) | MODEL: L16 pipe tip -&gt; seal face, body hex S1, nut S, bores D2 (pipe side) / D19 (swivel): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to the pipe tip) = L16 + the measured seal -&gt; nut face distance SEAL of the swivel; male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 6505); bore step at the body-hex mid-plane (ASSUMPTION, as 6505); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Air-Way FF6505 (s485, double-pass 2026-10-15, parts.air-way.com/api/series/485, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6505-08-08 (ORFS-p006-t04) | MODEL: L16 pipe tip -&gt; seal face, body hex S1, nut S, bores D2 (pipe side) / D19 (swivel): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to the pipe tip) = L16 + the measured seal -&gt; nut face distance SEAL of the swivel; male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 6505); bore step at the body-hex mid-plane (ASSUMPTION, as 6505); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
+          <t>Air-Way FF6505 (built to Air-Way); Brennan p6 DIFFERS (up to 0.160 in): overall length L16=1.99 vs Brennan L LGTH=2.150 | OMi parts file row 5608 (no dimensions)</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
-        <is>
-          <t>Air-Way FF6505 (built to Air-Way); Brennan p6 DIFFERS (up to 0.160 in): overall length L16=1.99 vs Brennan L LGTH=2.150 | OMi parts file row 5608 (no dimensions)</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
         <is>
           <t>FS6505-08-08</t>
         </is>
@@ -929,112 +921,109 @@
         <v>0.325</v>
       </c>
       <c r="W3" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.26238</v>
+      </c>
+      <c r="Y3" t="n">
         <v>45</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.50236</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AF3" t="n">
         <v>0.25118</v>
       </c>
-      <c r="Y3" t="n">
-        <v>0.26238</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.2985</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.50236</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.2947</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.05556</v>
-      </c>
       <c r="AG3" t="n">
-        <v>0.25118</v>
+        <v>0.28125</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.28125</v>
+        <v>0.2835</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.2835</v>
+        <v>1.845</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.845</v>
+        <v>0.281</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.281</v>
+        <v>0.715</v>
       </c>
       <c r="AL3" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="AN3" t="n">
         <v>0.715</v>
       </c>
-      <c r="AM3" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.825</v>
-      </c>
       <c r="AO3" t="n">
-        <v>0.715</v>
+        <v>0.87</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.87</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="AR3" t="n">
         <v>0.337</v>
       </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>FS6505-04-04</t>
+        </is>
+      </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>FS6505-04-04</t>
+          <t>ORFS Swivel Connector (female face-seal swivel x male pipe), 1/4-18 NPTF x 9/16-18 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>ORFS Swivel Connector (female face-seal swivel x male pipe), 1/4-18 NPTF x 9/16-18 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>FS6505</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>FS6505</t>
+          <t>1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF</t>
+          <t>9/16-18 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9/16-18 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>[BRENNAN-ONLY 2026-10-18] no Air-Way row (FF6505 has no row of this size) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L16@DRIVE: Brennan ORFS catalog p6 table ORFS-p006-t04 "FS6505 MP-FFSS STRAIGHT" row FS6505-04-04 col "L LGTH" = "1.520" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 200.1, page verified True) [Brennan = yes 2026-10-18] - pipe tip -&gt; swivel nut face; mapping: same-table check: 0/3 rows with an Air-Way value agree to rounding (3 differ, e.g. FS6505-08-08 1.99 vs 2.150); SHEX@HEX: Brennan ORFS catalog p6 table ORFS-p006-t04 "FS6505 MP-FFSS STRAIGHT" row FS6505-04-04 col "C HEX" = "0.688" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 200.1, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex; mapping: same-table check: 2/3 rows with an Air-Way value agree to rounding (1 differ, e.g. FS6505-16-16 1.61 vs 1.625); Q-FS-NUT: = Air-Way FF318-4 S 0.69 to rounding; S1HEX@HEX: Brennan ORFS catalog p6 table ORFS-p006-t04 "FS6505 MP-FFSS STRAIGHT" row FS6505-04-04 col "H HEX" = "0.625" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 200.1, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: same-table check: 2/3 rows with an Air-Way value agree to rounding (1 differ, e.g. FS6505-12-12 1.13 vs 1.250); D2@BORE: Brennan ORFS catalog p6 table ORFS-p006-t04 "FS6505 MP-FFSS STRAIGHT" row FS6505-04-04 col "A HOLE" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 200.1, page verified True) [Brennan = yes 2026-10-18] - pipe-end bore; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; D19@BORE: Brennan ORFS catalog p6 table ORFS-p006-t04 "FS6505 MP-FFSS STRAIGHT" row FS6505-04-04 col "B HOLE" = "0.165" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 200.1, page verified True) [Brennan = yes 2026-10-18] - swivel-end bore; mapping: same-table check: 2/3 rows with an Air-Way value agree to rounding (1 differ, e.g. FS6505-16-16 0.79 vs 0.783); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -04 = 0.5625 (PLAN.md s2 FS_THR / the -04 thread of every staged ORFS row); = Brennan "B THREAD" "9/16-18" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_A: Brennan ORFS catalog p6 table ORFS-p006-t04 "FS6505 MP-FFSS STRAIGHT" row FS6505-04-04 col "A THREAD" "1/4-18" in the table's format; $PRP@Thread_D: Brennan ORFS catalog p6 table ORFS-p006-t04 "FS6505 MP-FFSS STRAIGHT" row FS6505-04-04 col "B THREAD" "9/16-18" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p6 table ORFS-p006-t04 "FS6505 MP-FFSS STRAIGHT" row FS6505-04-04 col "TUBE O.D." "1/4" in the table's format | MODEL: L16 pipe tip -&gt; seal face, body hex S1, nut S, bores D2 (pipe side) / D19 (swivel): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to the pipe tip) = L16 + the measured seal -&gt; nut face distance SEAL of the swivel; male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 6505); bore step at the body-hex mid-plane (ASSUMPTION, as 6505); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] no Air-Way row (FF6505 has no row of this size) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L16@DRIVE: Brennan ORFS catalog p6 table ORFS-p006-t04 "FS6505 MP-FFSS STRAIGHT" row FS6505-04-04 col "L LGTH" = "1.520" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 200.1, page verified True) [Brennan = yes 2026-10-18] - pipe tip -&gt; swivel nut face; mapping: same-table check: 0/3 rows with an Air-Way value agree to rounding (3 differ, e.g. FS6505-08-08 1.99 vs 2.150); SHEX@HEX: Brennan ORFS catalog p6 table ORFS-p006-t04 "FS6505 MP-FFSS STRAIGHT" row FS6505-04-04 col "C HEX" = "0.688" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 200.1, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex; mapping: same-table check: 2/3 rows with an Air-Way value agree to rounding (1 differ, e.g. FS6505-16-16 1.61 vs 1.625); Q-FS-NUT: = Air-Way FF318-4 S 0.69 to rounding; S1HEX@HEX: Brennan ORFS catalog p6 table ORFS-p006-t04 "FS6505 MP-FFSS STRAIGHT" row FS6505-04-04 col "H HEX" = "0.625" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 200.1, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: same-table check: 2/3 rows with an Air-Way value agree to rounding (1 differ, e.g. FS6505-12-12 1.13 vs 1.250); D2@BORE: Brennan ORFS catalog p6 table ORFS-p006-t04 "FS6505 MP-FFSS STRAIGHT" row FS6505-04-04 col "A HOLE" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 200.1, page verified True) [Brennan = yes 2026-10-18] - pipe-end bore; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; D19@BORE: Brennan ORFS catalog p6 table ORFS-p006-t04 "FS6505 MP-FFSS STRAIGHT" row FS6505-04-04 col "B HOLE" = "0.165" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 200.1, page verified True) [Brennan = yes 2026-10-18] - swivel-end bore; mapping: same-table check: 2/3 rows with an Air-Way value agree to rounding (1 differ, e.g. FS6505-16-16 0.79 vs 0.783); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -04 = 0.5625 (PLAN.md s2 FS_THR / the -04 thread of every staged ORFS row); = Brennan "B THREAD" "9/16-18" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_A: Brennan ORFS catalog p6 table ORFS-p006-t04 "FS6505 MP-FFSS STRAIGHT" row FS6505-04-04 col "A THREAD" "1/4-18" in the table's format; $PRP@Thread_D: Brennan ORFS catalog p6 table ORFS-p006-t04 "FS6505 MP-FFSS STRAIGHT" row FS6505-04-04 col "B THREAD" "9/16-18" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p6 table ORFS-p006-t04 "FS6505 MP-FFSS STRAIGHT" row FS6505-04-04 col "TUBE O.D." "1/4" in the table's format | MODEL: L16 pipe tip -&gt; seal face, body hex S1, nut S, bores D2 (pipe side) / D19 (swivel): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to the pipe tip) = L16 + the measured seal -&gt; nut face distance SEAL of the swivel; male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 6505); bore step at the body-hex mid-plane (ASSUMPTION, as 6505); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
+          <t>no Air-Way FF6505 row of this size (Brennan prints it: Brennan-only stays MISSING) | OMi parts file row 5606 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p6 FS6505-04-04 ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
-        <is>
-          <t>no Air-Way FF6505 row of this size (Brennan prints it: Brennan-only stays MISSING) | OMi parts file row 5606 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p6 FS6505-04-04 ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
         <is>
           <t>FS6505-04-04</t>
         </is>
